--- a/Missing_Event_Stream_Inserts.xlsx
+++ b/Missing_Event_Stream_Inserts.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Inserts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary by Journey" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code status summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skipped conversions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible double counts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code status summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing Inserts'!$A$1:$N$285</definedName>
@@ -85,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -108,11 +110,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -139,6 +146,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P369"/>
+  <dimension ref="A1:R369"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -415,8 +429,10 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="46" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -500,6 +516,16 @@
           <t>Line in code</t>
         </is>
       </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>Step type</t>
+        </is>
+      </c>
+      <c r="R1" s="14" t="inlineStr">
+        <is>
+          <t>Events come from</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -551,6 +577,11 @@
           <t>no step id assigned</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>no step id assigned</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -600,6 +631,11 @@
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>no step id assigned</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>no step id assigned</t>
         </is>
@@ -653,6 +689,11 @@
           <t>no step id assigned</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>no step id assigned</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -707,6 +748,11 @@
       <c r="P5" t="n">
         <v>692</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -763,7 +809,12 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1266</v>
+        <v>1244</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -821,7 +872,12 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1272</v>
+        <v>1250</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -875,7 +931,12 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1278</v>
+        <v>1256</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -925,11 +986,16 @@
       <c r="N9" s="6" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>813</v>
+        <v>789</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -983,7 +1049,12 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>938</v>
+        <v>936</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1033,11 +1104,21 @@
       <c r="N11" s="6" t="n"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1202</v>
+        <v>1178</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>A6.B1.1, A6.B1.2, A6.B1.3, A6.B1.4, A6.B1.5, A6.B1.6</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1091,7 +1172,12 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1284</v>
+        <v>1262</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1145,7 +1231,12 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1324</v>
+        <v>1302</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1199,7 +1290,12 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1454</v>
+        <v>1436</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -1253,7 +1349,12 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1208</v>
+        <v>1184</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -1309,7 +1410,12 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1137</v>
+        <v>1112</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1359,11 +1465,21 @@
       <c r="N17" s="6" t="n"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1260</v>
+        <v>1238</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>A7.B1.1, A7.B1.2, A7.B1.3, A7.B1.4, A7.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1417,7 +1533,12 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1575</v>
+        <v>1563</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1471,7 +1592,12 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1254</v>
+        <v>1232</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1523,7 +1649,12 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4886</v>
+        <v>6572</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1577,7 +1708,12 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4887</v>
+        <v>6573</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1629,7 +1765,12 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4889</v>
+        <v>6575</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1681,7 +1822,12 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4888</v>
+        <v>6574</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1735,7 +1881,12 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4890</v>
+        <v>6576</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1789,7 +1940,12 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4804</v>
+        <v>6488</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1841,7 +1997,12 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4805</v>
+        <v>6489</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1893,7 +2054,12 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4806</v>
+        <v>6490</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1947,7 +2113,12 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4807</v>
+        <v>6491</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2001,7 +2172,12 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4884</v>
+        <v>6570</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2055,7 +2231,12 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4885</v>
+        <v>6571</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2109,7 +2290,12 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4891</v>
+        <v>6577</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2161,7 +2347,12 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4938</v>
+        <v>6633</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2215,7 +2406,12 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4892</v>
+        <v>6578</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2275,7 +2471,12 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4893</v>
+        <v>6579</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2333,11 +2534,16 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4899</v>
+        <v>6585</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2397,7 +2603,12 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4932</v>
+        <v>6627</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2457,7 +2668,12 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4935</v>
+        <v>6630</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2515,7 +2731,12 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3063</v>
+        <v>3279</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2571,7 +2792,12 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3069</v>
+        <v>3285</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2625,11 +2851,16 @@
       <c r="N40" s="3" t="n"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2987</v>
+        <v>3140</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2681,11 +2912,16 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3038</v>
+        <v>3230</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2737,11 +2973,16 @@
       <c r="N42" s="3" t="n"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3074</v>
+        <v>3290</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2795,7 +3036,12 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3091</v>
+        <v>3357</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2845,11 +3091,16 @@
       <c r="N44" s="6" t="n"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3083</v>
+        <v>3323</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2899,11 +3150,16 @@
       <c r="N45" s="6" t="n"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3095</v>
+        <v>3361</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2961,11 +3217,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3124</v>
+        <v>3396</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3025,7 +3286,12 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3166</v>
+        <v>3508</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3079,11 +3345,16 @@
       <c r="N48" s="3" t="n"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3142</v>
+        <v>3438</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3137,11 +3408,16 @@
       <c r="N49" s="3" t="n"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3151</v>
+        <v>3472</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3197,7 +3473,12 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3167</v>
+        <v>3509</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3249,11 +3530,16 @@
       <c r="N51" s="6" t="n"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3171</v>
+        <v>3513</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3303,11 +3589,16 @@
       <c r="N52" s="6" t="n"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3209</v>
+        <v>3595</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3357,11 +3648,21 @@
       <c r="N53" s="6" t="n"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3195</v>
+        <v>3583</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>HA5.B1.1, HA5.B1.2, HA5.B1.3, HA5.B1.4, HA5.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3411,11 +3712,16 @@
       <c r="N54" s="6" t="n"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3183</v>
+        <v>3549</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3475,11 +3781,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3230</v>
+        <v>3639</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3531,11 +3842,21 @@
       <c r="N56" s="3" t="n"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3293</v>
+        <v>3749</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>HA6.B1.1, HA6.B1.2, HA6.B1.3, HA6.B1.4, HA6.B1.5, HA6.B1.6</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3589,7 +3910,12 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3388</v>
+        <v>3891</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3647,11 +3973,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3389</v>
+        <v>3892</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3709,11 +4040,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3462</v>
+        <v>4042</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3771,11 +4107,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3401</v>
+        <v>3929</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3829,7 +4170,12 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3508</v>
+        <v>4134</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3883,7 +4229,12 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3294</v>
+        <v>3750</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3941,11 +4292,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3478</v>
+        <v>4080</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4005,11 +4361,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3270</v>
+        <v>3700</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4059,11 +4420,16 @@
       <c r="N65" s="6" t="n"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3298</v>
+        <v>3754</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4113,11 +4479,21 @@
       <c r="N66" s="6" t="n"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3318</v>
+        <v>3798</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>HA7.B1.1, HA7.B1.2, HA7.B1.3, HA7.B1.4, HA7.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4171,7 +4547,12 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3319</v>
+        <v>3799</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4225,7 +4606,12 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3319</v>
+        <v>3799</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4275,11 +4661,16 @@
       <c r="N69" s="6" t="n"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3323</v>
+        <v>3803</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4329,11 +4720,16 @@
       <c r="N70" s="6" t="n"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3323</v>
+        <v>3803</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4387,7 +4783,12 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3511</v>
+        <v>4137</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4441,7 +4842,12 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3512</v>
+        <v>4138</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4495,7 +4901,12 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3513</v>
+        <v>4139</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4547,7 +4958,12 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4502</v>
+        <v>6105</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4601,7 +5017,12 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4503</v>
+        <v>6106</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4653,7 +5074,12 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4505</v>
+        <v>6108</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4705,7 +5131,12 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4504</v>
+        <v>6107</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4759,7 +5190,12 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4506</v>
+        <v>6109</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4819,7 +5255,12 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4389</v>
+        <v>5904</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4871,7 +5312,12 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4409</v>
+        <v>5924</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -4931,7 +5377,12 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4420</v>
+        <v>5935</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4987,11 +5438,16 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4431</v>
+        <v>5946</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5047,11 +5503,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4450</v>
+        <v>5986</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -5109,11 +5570,16 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4470</v>
+        <v>6027</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5169,11 +5635,16 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4486</v>
+        <v>6066</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5227,7 +5698,12 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4501</v>
+        <v>6104</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5281,7 +5757,12 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4511</v>
+        <v>6114</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5335,7 +5816,12 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4507</v>
+        <v>6110</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5387,7 +5873,12 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>4508</v>
+        <v>6111</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5439,7 +5930,12 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4509</v>
+        <v>6112</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5493,7 +5989,12 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4510</v>
+        <v>6113</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5555,7 +6056,12 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>4515</v>
+        <v>6118</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5611,11 +6117,16 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>4535</v>
+        <v>6138</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5673,11 +6184,16 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>4554</v>
+        <v>6180</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5733,11 +6249,16 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4587</v>
+        <v>6222</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5793,11 +6314,16 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>4608</v>
+        <v>6266</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5851,7 +6377,12 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>4055</v>
+        <v>5316</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5903,7 +6434,12 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>4056</v>
+        <v>5317</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5955,7 +6491,12 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>4057</v>
+        <v>5318</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -6011,11 +6552,16 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>4058</v>
+        <v>5319</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -6073,11 +6619,16 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>4069</v>
+        <v>5354</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6133,11 +6684,16 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>4124</v>
+        <v>5446</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6195,11 +6751,21 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>4080</v>
+        <v>5389</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>HM4.B1.1, HM4.B1.2, HM4.B1.3, HM4.B1.4, HM4.B1.5, HM4.B1.6</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6255,11 +6821,16 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4234</v>
+        <v>5625</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -6315,11 +6886,16 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4303</v>
+        <v>5756</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6375,11 +6951,16 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4249</v>
+        <v>5662</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6435,11 +7016,16 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>4276</v>
+        <v>5709</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -6491,7 +7077,12 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4356</v>
+        <v>5850</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="25" customHeight="1">
@@ -6547,11 +7138,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>4095</v>
+        <v>5395</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -6607,11 +7203,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4319</v>
+        <v>5792</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -6663,7 +7264,12 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>4154</v>
+        <v>5499</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6715,7 +7321,12 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>4155</v>
+        <v>5500</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6771,11 +7382,16 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>4156</v>
+        <v>5501</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6829,7 +7445,12 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>4168</v>
+        <v>5536</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6885,11 +7506,16 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>4169</v>
+        <v>5537</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6937,11 +7563,21 @@
       <c r="N116" s="6" t="n"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>4188</v>
+        <v>5579</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>HM6.B1.1, HM6.B1.2, HM6.B1.3, HM6.B1.4, HM6.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6997,11 +7633,16 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>4357</v>
+        <v>5851</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -7053,7 +7694,12 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>4387</v>
+        <v>5902</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -7105,7 +7751,12 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>4388</v>
+        <v>5903</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -7163,11 +7814,16 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3514</v>
+        <v>4140</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -7223,7 +7879,12 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3552</v>
+        <v>4227</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -7281,11 +7942,16 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3521</v>
+        <v>4172</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="123" ht="25" customHeight="1">
@@ -7340,7 +8006,12 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3550</v>
+        <v>4225</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -7394,7 +8065,12 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>3551</v>
+        <v>4226</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -7452,11 +8128,16 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>3653</v>
+        <v>4437</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -7514,11 +8195,16 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3668</v>
+        <v>4476</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -7572,11 +8258,16 @@
       <c r="N127" s="3" t="n"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3556</v>
+        <v>4231</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -7628,11 +8319,16 @@
       <c r="N128" s="3" t="n"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3571</v>
+        <v>4272</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -7686,11 +8382,16 @@
       <c r="N129" s="3" t="n"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3585</v>
+        <v>4312</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -7740,11 +8441,21 @@
       <c r="N130" s="6" t="n"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>3621</v>
+        <v>4394</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>HR2.B1.1, HR2.B1.2, HR2.B1.3</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -7792,11 +8503,16 @@
       <c r="N131" s="6" t="n"/>
       <c r="O131" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>3889</v>
+        <v>4854</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -7848,7 +8564,12 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3900</v>
+        <v>4892</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -7900,7 +8621,12 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3908</v>
+        <v>4900</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -7948,11 +8674,16 @@
       <c r="N134" s="6" t="n"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3912</v>
+        <v>4904</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -8002,11 +8733,16 @@
       <c r="N135" s="6" t="n"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>3644</v>
+        <v>4402</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -8054,11 +8790,16 @@
       <c r="N136" s="6" t="n"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>3918</v>
+        <v>4937</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -8106,11 +8847,16 @@
       <c r="N137" s="6" t="n"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>3925</v>
+        <v>4971</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -8158,11 +8904,16 @@
       <c r="N138" s="6" t="n"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P138" t="n">
-        <v>3932</v>
+        <v>5005</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -8220,11 +8971,16 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3600</v>
+        <v>4349</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -8282,11 +9038,21 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3711</v>
+        <v>4590</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>HR3.B1.1, HR3.B1.2</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -8334,11 +9100,16 @@
       <c r="N141" s="6" t="n"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>3939</v>
+        <v>5038</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -8390,7 +9161,12 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3947</v>
+        <v>5069</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -8442,7 +9218,12 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3948</v>
+        <v>5070</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -8498,11 +9279,16 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>3949</v>
+        <v>5071</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -8558,11 +9344,16 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3964</v>
+        <v>5111</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -8612,11 +9403,16 @@
       <c r="N146" s="6" t="n"/>
       <c r="O146" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>3735</v>
+        <v>4611</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -8670,11 +9466,16 @@
       <c r="N147" s="3" t="n"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>3684</v>
+        <v>4517</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -8728,11 +9529,16 @@
       <c r="N148" s="3" t="n"/>
       <c r="O148" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>3698</v>
+        <v>4554</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -8786,7 +9592,12 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3707</v>
+        <v>4586</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -8836,11 +9647,16 @@
       <c r="N150" s="6" t="n"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>3742</v>
+        <v>4641</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -8898,11 +9714,21 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>3750</v>
+        <v>4672</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>HR4.B2.1, HR4.B2.2, HR4.B2.3, HR4.B2.4, HR4.B2.5, HR4.B2.6</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -8950,11 +9776,16 @@
       <c r="N152" s="6" t="n"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3980</v>
+        <v>5152</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -9002,11 +9833,16 @@
       <c r="N153" s="6" t="n"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>3996</v>
+        <v>5191</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -9058,7 +9894,12 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>4026</v>
+        <v>5266</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -9110,7 +9951,12 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>4008</v>
+        <v>5225</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -9158,11 +10004,16 @@
       <c r="N156" s="6" t="n"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>4012</v>
+        <v>5229</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -9214,7 +10065,12 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>4051</v>
+        <v>5312</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="158" ht="25" customHeight="1">
@@ -9276,7 +10132,12 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3801</v>
+        <v>4709</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -9324,11 +10185,16 @@
       <c r="N159" s="6" t="n"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P159" t="n">
-        <v>4030</v>
+        <v>5270</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -9378,11 +10244,16 @@
       <c r="N160" s="3" t="n"/>
       <c r="O160" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>3809</v>
+        <v>4717</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -9430,11 +10301,16 @@
       <c r="N161" s="6" t="n"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>3826</v>
+        <v>4760</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -9486,7 +10362,12 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>3843</v>
+        <v>4799</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -9538,7 +10419,12 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>3844</v>
+        <v>4800</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -9586,11 +10472,21 @@
       <c r="N164" s="6" t="n"/>
       <c r="O164" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P164" t="n">
-        <v>3869</v>
+        <v>4846</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>HR6.B1.1, HR6.B1.2, HR6.B1.3, HR6.B1.4, HR6.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -9642,7 +10538,12 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>4052</v>
+        <v>5313</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -9694,7 +10595,12 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>4053</v>
+        <v>5314</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -9746,7 +10652,12 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>4054</v>
+        <v>5315</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -9794,11 +10705,16 @@
       <c r="N168" s="6" t="n"/>
       <c r="O168" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>3848</v>
+        <v>4804</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -9850,7 +10766,12 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>4709</v>
+        <v>6391</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -9902,7 +10823,12 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>4710</v>
+        <v>6392</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -9954,7 +10880,12 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>4711</v>
+        <v>6393</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -10006,7 +10937,12 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>4712</v>
+        <v>6394</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -10060,7 +10996,12 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>4704</v>
+        <v>6386</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -10112,7 +11053,12 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>4741</v>
+        <v>6424</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -10164,7 +11110,12 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>4771</v>
+        <v>6455</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -10216,7 +11167,12 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>4742</v>
+        <v>6425</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -10268,7 +11224,12 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>4743</v>
+        <v>6426</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -10320,7 +11281,12 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>4803</v>
+        <v>6487</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -10372,7 +11338,12 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>4705</v>
+        <v>6387</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -10426,7 +11397,12 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>4706</v>
+        <v>6388</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -10480,7 +11456,12 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>4707</v>
+        <v>6389</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -10534,7 +11515,12 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>4708</v>
+        <v>6390</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -10588,7 +11574,12 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1621</v>
+        <v>1611</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -10642,7 +11633,12 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1695</v>
+        <v>1687</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -10696,7 +11692,12 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1696</v>
+        <v>1688</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -10750,7 +11751,12 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2279</v>
+        <v>2258</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="187" ht="25" customHeight="1">
@@ -10804,7 +11810,12 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1869</v>
+        <v>1863</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -10860,7 +11871,12 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1764</v>
+        <v>1778</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -10918,11 +11934,16 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2459</v>
+        <v>2444</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -10980,11 +12001,16 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2501</v>
+        <v>2533</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -11042,11 +12068,16 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2596</v>
+        <v>2652</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -11104,11 +12135,16 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2610</v>
+        <v>2690</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -11166,11 +12202,16 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2624</v>
+        <v>2728</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -11228,11 +12269,16 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2699</v>
+        <v>2827</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -11286,7 +12332,12 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2040</v>
+        <v>2016</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -11340,7 +12391,12 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2004</v>
+        <v>2000</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -11394,7 +12450,12 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2041</v>
+        <v>2017</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -11444,11 +12505,21 @@
       <c r="N198" s="6" t="n"/>
       <c r="O198" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2082</v>
+        <v>2058</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>R4.B2.1, R4.B2.2, R4.B2.3, R4.B2.4, R4.B2.5, R4.B2.6</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -11502,7 +12573,12 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2795</v>
+        <v>2947</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="200" ht="25" customHeight="1">
@@ -11556,7 +12632,12 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2722</v>
+        <v>2874</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -11606,11 +12687,21 @@
       <c r="N201" s="6" t="n"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>2718</v>
+        <v>2870</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>R6.B1.1, R6.B1.2, R6.B1.3, R6.B1.4, R6.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -11664,7 +12755,12 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>2947</v>
+        <v>3099</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -11718,7 +12814,12 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2948</v>
+        <v>3100</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -11780,7 +12881,12 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2711</v>
+        <v>2863</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -11834,7 +12940,12 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1620</v>
+        <v>1610</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -11888,7 +12999,12 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>6091</v>
+        <v>8007</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -11944,7 +13060,12 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>6060</v>
+        <v>7974</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -12000,7 +13121,12 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>6094</v>
+        <v>8010</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -12056,7 +13182,12 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>6092</v>
+        <v>8008</v>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -12112,7 +13243,12 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>6093</v>
+        <v>8009</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -12166,7 +13302,12 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>5525</v>
+        <v>7445</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -12218,7 +13359,12 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>5694</v>
+        <v>7593</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -12272,7 +13418,12 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>5664</v>
+        <v>7563</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -12322,11 +13473,21 @@
       <c r="N214" s="3" t="n"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P214" t="n">
-        <v>5665</v>
+        <v>7564</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>VA6.B1.1, VA6.B1.2, VA6.B1.3, VA6.B1.4, VA6.B1.5, VA6.B1.6</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -12378,7 +13539,12 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>5695</v>
+        <v>7594</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -12430,7 +13596,12 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>5696</v>
+        <v>7595</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -12482,7 +13653,12 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>5697</v>
+        <v>7596</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -12534,7 +13710,12 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>5794</v>
+        <v>7696</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -12594,7 +13775,12 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>5669</v>
+        <v>7568</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -12648,7 +13834,12 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>5692</v>
+        <v>7591</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -12696,11 +13887,21 @@
       <c r="N221" s="6" t="n"/>
       <c r="O221" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>5693</v>
+        <v>7592</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>VA7.B1.1, VA7.B1.2, VA7.B1.3, VA7.B1.4, VA7.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -12752,7 +13953,12 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>5868</v>
+        <v>7772</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -12804,7 +14010,12 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>5869</v>
+        <v>7773</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -12856,7 +14067,12 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>5931</v>
+        <v>7836</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -12910,7 +14126,12 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>5932</v>
+        <v>7837</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -12962,7 +14183,12 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>5934</v>
+        <v>7839</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -13014,7 +14240,12 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>5935</v>
+        <v>7840</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -13066,7 +14297,12 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>5933</v>
+        <v>7838</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -13120,7 +14356,12 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>5936</v>
+        <v>7841</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -13174,7 +14415,12 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>5924</v>
+        <v>7829</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -13226,7 +14472,12 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>5925</v>
+        <v>7830</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -13278,7 +14529,12 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>5926</v>
+        <v>7831</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -13330,7 +14586,12 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>5927</v>
+        <v>7832</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -13384,7 +14645,12 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>5928</v>
+        <v>7833</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -13436,7 +14702,12 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>5929</v>
+        <v>7834</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -13490,7 +14761,12 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>5930</v>
+        <v>7835</v>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -13544,7 +14820,12 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>5937</v>
+        <v>7842</v>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -13596,7 +14877,12 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>5984</v>
+        <v>7898</v>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -13650,7 +14936,12 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>5938</v>
+        <v>7843</v>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -13710,7 +15001,12 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>5939</v>
+        <v>7844</v>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -13768,11 +15064,16 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P241" t="n">
-        <v>5945</v>
+        <v>7850</v>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -13832,7 +15133,12 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>5978</v>
+        <v>7892</v>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -13892,7 +15198,12 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>5981</v>
+        <v>7895</v>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -13946,7 +15257,12 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>5903</v>
+        <v>7808</v>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -13998,7 +15314,12 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>5904</v>
+        <v>7809</v>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -14050,7 +15371,12 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>5905</v>
+        <v>7810</v>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -14104,7 +15430,12 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>5906</v>
+        <v>7811</v>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -14152,11 +15483,21 @@
       <c r="N248" s="6" t="n"/>
       <c r="O248" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P248" t="n">
-        <v>5907</v>
+        <v>7812</v>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>VM3.B1.1, VM3.B1.2, VM3.B1.3, VM3.B1.4, VM3.B1.5, VM3.B1.6</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -14208,7 +15549,12 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>5913</v>
+        <v>7818</v>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -14260,7 +15606,12 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>5916</v>
+        <v>7821</v>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -14312,7 +15663,12 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>5914</v>
+        <v>7819</v>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -14364,7 +15720,12 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>5915</v>
+        <v>7820</v>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -14416,7 +15777,12 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>5918</v>
+        <v>7823</v>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="254" ht="25" customHeight="1">
@@ -14468,7 +15834,12 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>5908</v>
+        <v>7813</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -14520,7 +15891,12 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>5917</v>
+        <v>7822</v>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -14572,7 +15948,12 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>5909</v>
+        <v>7814</v>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -14624,7 +16005,12 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>5910</v>
+        <v>7815</v>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -14674,11 +16060,21 @@
       <c r="N258" s="3" t="n"/>
       <c r="O258" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P258" t="n">
-        <v>5911</v>
+        <v>7816</v>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>VM6.B1.1, VM6.B1.2, VM6.B1.3, VM6.B1.4, VM6.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -14730,7 +16126,12 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>5919</v>
+        <v>7824</v>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -14782,7 +16183,12 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>5920</v>
+        <v>7825</v>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -14834,7 +16240,12 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>5921</v>
+        <v>7826</v>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -14886,7 +16297,12 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>5922</v>
+        <v>7827</v>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -14938,7 +16354,12 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>5923</v>
+        <v>7828</v>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -14998,7 +16419,12 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>5031</v>
+        <v>6728</v>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -15054,11 +16480,16 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P265" t="n">
-        <v>5225</v>
+        <v>6958</v>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -15114,11 +16545,16 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P266" t="n">
-        <v>5239</v>
+        <v>6995</v>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -15174,11 +16610,16 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P267" t="n">
-        <v>5267</v>
+        <v>7047</v>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -15230,7 +16671,12 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>5303</v>
+        <v>7107</v>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -15282,7 +16728,12 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>5304</v>
+        <v>7108</v>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -15342,7 +16793,12 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>5098</v>
+        <v>6793</v>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -15402,11 +16858,16 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P271" t="n">
-        <v>5035</v>
+        <v>6732</v>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -15470,7 +16931,12 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>5048</v>
+        <v>6768</v>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -15522,7 +16988,12 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>5064</v>
+        <v>6784</v>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -15584,7 +17055,12 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>5117</v>
+        <v>6812</v>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -15636,7 +17112,12 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>5305</v>
+        <v>7109</v>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -15692,11 +17173,16 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P276" t="n">
-        <v>5306</v>
+        <v>7110</v>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -15752,11 +17238,16 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P277" t="n">
-        <v>5376</v>
+        <v>7227</v>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -15812,11 +17303,16 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P278" t="n">
-        <v>5324</v>
+        <v>7152</v>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -15868,7 +17364,12 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>5375</v>
+        <v>7226</v>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -15920,7 +17421,12 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>5454</v>
+        <v>7352</v>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="281" ht="25" customHeight="1">
@@ -15976,11 +17482,16 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P281" t="n">
-        <v>5164</v>
+        <v>6854</v>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -16036,11 +17547,16 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P282" t="n">
-        <v>5395</v>
+        <v>7269</v>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -16096,11 +17612,16 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P283" t="n">
-        <v>5215</v>
+        <v>6924</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -16150,11 +17671,21 @@
       <c r="N284" s="3" t="n"/>
       <c r="O284" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P284" t="n">
-        <v>5224</v>
+        <v>6957</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>VR6.B1.1, VR6.B1.2, VR6.B1.3, VR6.B1.4, VR6.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -16210,11 +17741,16 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P285" t="n">
-        <v>5455</v>
+        <v>7353</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -16268,6 +17804,11 @@
       <c r="P286" t="n">
         <v>499</v>
       </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16306,6 +17847,11 @@
       <c r="P287" t="n">
         <v>529</v>
       </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16353,6 +17899,11 @@
       <c r="P288" t="n">
         <v>564</v>
       </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16397,6 +17948,11 @@
       <c r="P289" t="n">
         <v>597</v>
       </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16438,6 +17994,11 @@
       <c r="P290" t="n">
         <v>632</v>
       </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16479,6 +18040,11 @@
       <c r="P291" t="n">
         <v>662</v>
       </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16531,6 +18097,11 @@
       <c r="P292" t="n">
         <v>698</v>
       </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16572,6 +18143,11 @@
       <c r="P293" t="n">
         <v>744</v>
       </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16607,12 +18183,22 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P294" t="n">
         <v>780</v>
       </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>A3.B1.1, A3.B1.2</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16663,7 +18249,12 @@
         </is>
       </c>
       <c r="P295" t="n">
-        <v>831</v>
+        <v>829</v>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -16715,7 +18306,12 @@
         </is>
       </c>
       <c r="P296" t="n">
-        <v>869</v>
+        <v>867</v>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -16759,7 +18355,12 @@
         </is>
       </c>
       <c r="P297" t="n">
-        <v>902</v>
+        <v>900</v>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -16800,7 +18401,12 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>944</v>
+        <v>942</v>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -16841,7 +18447,12 @@
         </is>
       </c>
       <c r="P299" t="n">
-        <v>975</v>
+        <v>973</v>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -16881,11 +18492,21 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P300" t="n">
-        <v>1007</v>
+        <v>1005</v>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>A5.B1.1, A5.B1.2, A5.B1.3, A5.B1.4, A5.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -16929,7 +18550,12 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>1040</v>
+        <v>1014</v>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -16976,7 +18602,12 @@
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1072</v>
+        <v>1046</v>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -17020,7 +18651,12 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>1214</v>
+        <v>1190</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -17061,7 +18697,12 @@
         </is>
       </c>
       <c r="P304" t="n">
-        <v>1290</v>
+        <v>1268</v>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -17102,7 +18743,12 @@
         </is>
       </c>
       <c r="P305" t="n">
-        <v>1330</v>
+        <v>1308</v>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -17143,7 +18789,12 @@
         </is>
       </c>
       <c r="P306" t="n">
-        <v>1368</v>
+        <v>1348</v>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -17184,7 +18835,12 @@
         </is>
       </c>
       <c r="P307" t="n">
-        <v>1403</v>
+        <v>1383</v>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -17225,7 +18881,12 @@
         </is>
       </c>
       <c r="P308" t="n">
-        <v>1460</v>
+        <v>1442</v>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -17266,7 +18927,12 @@
         </is>
       </c>
       <c r="P309" t="n">
-        <v>1498</v>
+        <v>1482</v>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -17307,7 +18973,12 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>1537</v>
+        <v>1523</v>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -17348,7 +19019,12 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>1581</v>
+        <v>1569</v>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -17389,7 +19065,12 @@
         </is>
       </c>
       <c r="P312" t="n">
-        <v>1622</v>
+        <v>1612</v>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -17438,7 +19119,12 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1637</v>
+        <v>1627</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -17482,7 +19168,12 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>1666</v>
+        <v>1658</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -17529,11 +19220,16 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1697</v>
+        <v>1689</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -17585,7 +19281,12 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1728</v>
+        <v>1742</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -17622,11 +19323,21 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P317" t="n">
-        <v>1800</v>
+        <v>1814</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>R2.B1.1, R2.B1.2, R2.B1.3, R2.B1.4</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -17667,7 +19378,12 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1829</v>
+        <v>1823</v>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -17719,7 +19435,12 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1875</v>
+        <v>1869</v>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -17766,7 +19487,12 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>1904</v>
+        <v>1898</v>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -17802,7 +19528,12 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1940</v>
+        <v>1934</v>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -17840,7 +19571,12 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1972</v>
+        <v>1967</v>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -17877,11 +19613,21 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P323" t="n">
-        <v>2011</v>
+        <v>2007</v>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>R3.B1.1, R3.B1.2, R3.B1.3, R3.B1.4</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -17922,7 +19668,12 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>2047</v>
+        <v>2023</v>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -17966,7 +19717,12 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>2088</v>
+        <v>2064</v>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -18010,7 +19766,12 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>2125</v>
+        <v>2101</v>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -18051,7 +19812,12 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>2162</v>
+        <v>2138</v>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -18095,7 +19861,12 @@
         </is>
       </c>
       <c r="P328" t="n">
-        <v>2206</v>
+        <v>2182</v>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -18136,7 +19907,12 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>2252</v>
+        <v>2230</v>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -18177,7 +19953,12 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>2285</v>
+        <v>2264</v>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -18218,7 +19999,12 @@
         </is>
       </c>
       <c r="P331" t="n">
-        <v>2312</v>
+        <v>2292</v>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -18259,7 +20045,12 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>2346</v>
+        <v>2327</v>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -18300,7 +20091,12 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>2374</v>
+        <v>2356</v>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -18341,7 +20137,12 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>2402</v>
+        <v>2385</v>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -18382,7 +20183,12 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>2430</v>
+        <v>2414</v>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -18429,11 +20235,16 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P336" t="n">
-        <v>2473</v>
+        <v>2482</v>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -18474,7 +20285,12 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>2727</v>
+        <v>2879</v>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -18515,7 +20331,12 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>2764</v>
+        <v>2916</v>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -18556,7 +20377,12 @@
         </is>
       </c>
       <c r="P339" t="n">
-        <v>2801</v>
+        <v>2953</v>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -18597,7 +20423,12 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>2836</v>
+        <v>2988</v>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -18638,7 +20469,12 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>2868</v>
+        <v>3020</v>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -18679,7 +20515,12 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>2915</v>
+        <v>3067</v>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -18720,7 +20561,12 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>2954</v>
+        <v>3106</v>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -18764,11 +20610,16 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P344" t="n">
-        <v>3012</v>
+        <v>3181</v>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -18806,7 +20657,12 @@
         </is>
       </c>
       <c r="P345" t="n">
-        <v>3051</v>
+        <v>3267</v>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -18855,11 +20711,16 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P346" t="n">
-        <v>3424</v>
+        <v>3978</v>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -18912,7 +20773,12 @@
         </is>
       </c>
       <c r="P347" t="n">
-        <v>4189</v>
+        <v>5580</v>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -18959,7 +20825,12 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>4630</v>
+        <v>6311</v>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -19003,7 +20874,12 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>4662</v>
+        <v>6343</v>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -19044,7 +20920,12 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>4713</v>
+        <v>6395</v>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -19088,7 +20969,12 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>4808</v>
+        <v>6492</v>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -19140,7 +21026,12 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>4939</v>
+        <v>6634</v>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -19184,7 +21075,12 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>4975</v>
+        <v>6671</v>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -19225,7 +21121,12 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>5002</v>
+        <v>6699</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -19262,11 +21163,21 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P355" t="n">
-        <v>5065</v>
+        <v>6785</v>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>VR3.B1.1, VR3.B1.2</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -19315,11 +21226,21 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P356" t="n">
-        <v>5120</v>
+        <v>6815</v>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>VR4.B2.1, VR4.B2.2, VR4.B2.3, VR4.B2.4, VR4.B2.5, VR4.B2.6</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -19371,7 +21292,12 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>5491</v>
+        <v>7411</v>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -19418,7 +21344,12 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>5560</v>
+        <v>7480</v>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -19470,7 +21401,12 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>5600</v>
+        <v>7520</v>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -19507,11 +21443,21 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>insert query</t>
+          <t>block header, no insert by design</t>
         </is>
       </c>
       <c r="P360" t="n">
-        <v>5636</v>
+        <v>7557</v>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Block header</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>VA5.B1.1, VA5.B1.2, VA5.B1.3, VA5.B1.4, VA5.B1.5</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -19565,7 +21511,12 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>5698</v>
+        <v>7597</v>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -19606,7 +21557,12 @@
         </is>
       </c>
       <c r="P362" t="n">
-        <v>5732</v>
+        <v>7632</v>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -19647,7 +21603,12 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>5760</v>
+        <v>7661</v>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -19688,7 +21649,12 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>5798</v>
+        <v>7700</v>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -19729,7 +21695,12 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>5832</v>
+        <v>7735</v>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -19772,7 +21743,12 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>5912</v>
+        <v>7817</v>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -19816,7 +21792,12 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>5985</v>
+        <v>7899</v>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -19868,7 +21849,12 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>6013</v>
+        <v>7927</v>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -19912,7 +21898,12 @@
         </is>
       </c>
       <c r="P369" t="n">
-        <v>6064</v>
+        <v>7979</v>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20667,7 +22658,2743 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Line in code</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>Why it was left as it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HA0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3094</v>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>It reads stg.A0_MFQ_genesys_link, which is built filtered to queueName = 'INBOUND_SALES_MOTOR', so there is no Home population and no Home equivalent staging table in the notebook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HA0.F1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>It reads stg.HA0F1_genesys_inbound_call_duration_summary, which is never created anywhere in the notebook, so its columns cannot be relied on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HA1.F1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3082</v>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>The step text is about outbound campaigns sent to quotes that never got a price but the query is an anti join that returns HFQ quotes with no campaign row at all and never tests for a price, so the step and the query disagree about what is being measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HC1a</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4420</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>The only date column the notebook ever names on edw.tbl_fact_policy_mtc is EffectiveDate, which is pinned to the single snapshot date 2026-07-31, so there is no event timestamp to use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HC1a.F1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4440</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>The cell is an exploratory select star with no grain, no timestamp and a volume of zero rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HC1b.F1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4451</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>The same exploratory select star as HC1a.F1, with no grain, no timestamp and a volume of zero rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HD1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4546</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>The step is the inbound call asking for a document but the query counts documents emailed or transmitted, which is exactly what HD2 already measures, so the step id and the query disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HM4.B1.1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4220</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>The cell holds two competing queries with the author's own results of 0 and 28 pencilled against them, so it is an investigation note and there is no single query that defines the step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HR2.B1.2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3931</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>This is an exploratory select * with a limit 100 and the cell itself says the record to pick for the event stream has not been decided, so there is no clear grain to insert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R3b.F1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>The cell holds only the table name stg.R0_genesys_derived_data with no select, filters or grain, so there is nothing to convert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RO.F2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1638</v>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>The product is not given so PolicyTypeGroup cannot be set, and stg.motorclaims is not built anywhere in the notebook, its only date column ClaimDate being an integer in yyyymmdd form rather than a timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TA3a</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6106</v>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>The cell contains only a note about the number covering both acquisition and renewal plus a stray group by line, so there is no query to convert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VA6.B1.F1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5709</v>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>The cell holds the Home renewals chase query against edw.EXP_MyChill_Chase_Daily_Snapshot_Home and stg.R0_HomePoliciesEligibleForRenewals filtered to PolicyTypeGroup Home and PolicyType Renewals, so it does not measure the Van acquisition step it sits under.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VR3.O1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5136</v>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>The cell is an exploratory select star with a limit of 10 against stg.VanRenewalsJuly, so it has no event grain and no timestamp to use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VR3b</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5086</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>The query counts policies with a receipt document emailed or transmitted, which is not a measure of renewing on an inbound call, and the notebook itself flags the cell as not enough volume.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Journey</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Step description</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Fabric volume</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Code status</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Why it is flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HA6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Documents requested</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HA6.B1.1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Document request issued</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>HA7</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Policy documents dispatched</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume; ancestor, same wording and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HA7.B1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Policy fulfilment</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ancestor and same volume; ancestor, same wording and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HA7.B1.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Policy documents dispatched</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ancestor and same volume; ancestor, same wording and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HA7.B1.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Document pack dispatched</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ancestor and same volume; ancestor, same wording and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HA7.B1.3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Customer receipt, implicit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ancestor and same volume; ancestor, same wording and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>HA6.B1</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Document intake</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HA6.B1.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Customer submits documents</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>HC.IN1</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Upstream feed: Acquisition</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HC.IN2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Upstream feed: Acquisition</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>HC.IN3</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Upstream feed: Renewal</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HC.IN4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Upstream feed: Renewal</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>HM.V6</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HM4b.B1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>HR6</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Renewal documents dispatched</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HR6.B1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Policy fulfilment</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HR6.B1.1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Policy documents dispatched</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>HR2.B1</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Online re-quote for another price</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HR2.B1.1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Re-quote started from the renewal price</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>HR3.B1</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>This year lapsed</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HR3.B1.2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lapse CRM sequence runs</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>HR4.B2</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Documents requested</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HR4.B2.4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Chase, first reminder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HR4.B2.F1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Chases before the customer submits, and documents never submitted</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Documents requested</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A6.B1.1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Document request issued</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Cert and disc sent</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>12</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A7.B1.2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Document pack dispatched</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A7.B1.3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Customer receipt, implicit</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>A6.B1</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Document intake</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A6.B1.2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Customer submits documents</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>A7.B1</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Cert and disc dispatch</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>3918</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A7.B1.1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cert and disc dispatched</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3918</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>A5.B1.5</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Payment confirmed on the loan path</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>15</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>A5.B1.PC5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Payment confirmed on the loan path</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>M.V6</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>16</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M4b.B1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Cert and disc sent</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>11559</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>R6.B1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cert and disc dispatch</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>11559</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>17</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>R6.B1.1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Cert and disc dispatched</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11559</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>R3.B1</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>This year lapsed</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>R3.B1.2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lapse CRM sequence runs</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>VA6.B1</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Document intake</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VA6.B1.2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Customer submits documents</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>VA7.B1</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Cert and disc dispatch</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VA7.B1.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Replacement requested</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>insert query</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>VC.IN1</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Upstream feed: Acquisition</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>21</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VC.IN2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Upstream feed: Acquisition</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>VC.IN3</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Upstream feed: Renewal</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>22</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VC.IN4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Upstream feed: Renewal</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>VM.V6</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>23</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VM4b.B1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Payment schedule change</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>not in code</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>same wording</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>VM3.B1</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Document intake</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>24</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mta</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VM3.B1.2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>sub-step</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Customer submits documents</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ancestor and same volume</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20675,8 +25402,9 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20697,20 +25425,25 @@
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
+          <t>block header</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
           <t>insert query</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>count query</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>other SQL, no insert</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>empty</t>
         </is>
@@ -20731,16 +25464,19 @@
         <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -20767,6 +25503,9 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20785,15 +25524,18 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -20821,6 +25563,9 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20848,6 +25593,9 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20859,22 +25607,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mta</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>17</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -20890,19 +25641,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>15</v>
+      <c r="H8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -20920,16 +25674,19 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
+      <c r="H9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -20956,6 +25713,9 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20980,9 +25740,12 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21010,6 +25773,9 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21031,12 +25797,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21048,23 +25817,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mta</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>11</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10</v>
+      <c r="H14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -21082,15 +25854,18 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>22</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -21109,16 +25884,19 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="n">
-        <v>10</v>
+      <c r="H16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -21145,6 +25923,9 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21172,6 +25953,9 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21199,6 +25983,9 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21226,6 +26013,9 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21237,14 +26027,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mta</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -21253,7 +26043,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -21271,16 +26064,19 @@
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -21298,17 +26094,20 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21334,30 +26133,66 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="n">
         <v>363</v>
       </c>
-      <c r="D25" t="n">
-        <v>81</v>
-      </c>
-      <c r="E25" t="n">
-        <v>85</v>
-      </c>
-      <c r="F25" t="n">
-        <v>28</v>
-      </c>
-      <c r="G25" t="n">
-        <v>169</v>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>166</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Missing_Event_Stream_Inserts.xlsx
+++ b/Missing_Event_Stream_Inserts.xlsx
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>6572</v>
+        <v>6838</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6573</v>
+        <v>6839</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6575</v>
+        <v>6841</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>6574</v>
+        <v>6840</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6576</v>
+        <v>6842</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>6488</v>
+        <v>6754</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6489</v>
+        <v>6755</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6490</v>
+        <v>6756</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>6491</v>
+        <v>6757</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>6570</v>
+        <v>6836</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>6571</v>
+        <v>6837</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>6577</v>
+        <v>6843</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>6633</v>
+        <v>6939</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2402,11 +2402,11 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>6578</v>
+        <v>6844</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>6579</v>
+        <v>6885</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>6585</v>
+        <v>6891</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6627</v>
+        <v>6933</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6630</v>
+        <v>6936</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2727,11 +2727,11 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3279</v>
+        <v>3362</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3285</v>
+        <v>3413</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3140</v>
+        <v>3191</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3230</v>
+        <v>3281</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3290</v>
+        <v>3459</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3357</v>
+        <v>3526</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3323</v>
+        <v>3492</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3361</v>
+        <v>3530</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3396</v>
+        <v>3565</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3508</v>
+        <v>3677</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3438</v>
+        <v>3607</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3472</v>
+        <v>3641</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3509</v>
+        <v>3678</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3513</v>
+        <v>3682</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3595</v>
+        <v>3764</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3549</v>
+        <v>3718</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3639</v>
+        <v>3808</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3891</v>
+        <v>4060</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3892</v>
+        <v>4061</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>4042</v>
+        <v>4211</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3929</v>
+        <v>4098</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>4134</v>
+        <v>4303</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3750</v>
+        <v>3919</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4080</v>
+        <v>4249</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3700</v>
+        <v>3869</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3754</v>
+        <v>3923</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3799</v>
+        <v>3968</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3799</v>
+        <v>3968</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3803</v>
+        <v>3972</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3803</v>
+        <v>3972</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4137</v>
+        <v>4306</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4138</v>
+        <v>4307</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4139</v>
+        <v>4308</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>6105</v>
+        <v>6349</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>6106</v>
+        <v>6350</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>6108</v>
+        <v>6352</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>6107</v>
+        <v>6351</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>6109</v>
+        <v>6353</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -5251,11 +5251,11 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>5904</v>
+        <v>6106</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5308,11 +5308,11 @@
       <c r="N80" s="6" t="n"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5924</v>
+        <v>6153</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5373,11 +5373,8 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
-        </is>
-      </c>
-      <c r="P81" t="n">
-        <v>5935</v>
+          <t>removed from code, duplicate of HC1a.F1</t>
+        </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5442,7 +5439,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>5946</v>
+        <v>6190</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -5507,7 +5504,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>5986</v>
+        <v>6230</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5574,7 +5571,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>6027</v>
+        <v>6271</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -5639,7 +5636,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>6066</v>
+        <v>6310</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -5698,7 +5695,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>6104</v>
+        <v>6348</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -5757,7 +5754,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>6114</v>
+        <v>6358</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -5816,7 +5813,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>6110</v>
+        <v>6354</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -5873,7 +5870,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>6111</v>
+        <v>6355</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -5930,7 +5927,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>6112</v>
+        <v>6356</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -5989,7 +5986,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>6113</v>
+        <v>6357</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6052,11 +6049,11 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>6118</v>
+        <v>6362</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -6121,7 +6118,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>6138</v>
+        <v>6404</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6188,7 +6185,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>6180</v>
+        <v>6446</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -6253,7 +6250,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>6222</v>
+        <v>6488</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6318,7 +6315,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>6266</v>
+        <v>6532</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6377,7 +6374,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>5316</v>
+        <v>5513</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6434,7 +6431,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>5317</v>
+        <v>5514</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6491,7 +6488,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>5318</v>
+        <v>5515</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6556,7 +6553,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>5319</v>
+        <v>5516</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6623,7 +6620,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>5354</v>
+        <v>5551</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -6688,7 +6685,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>5446</v>
+        <v>5643</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -6825,7 +6822,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>5625</v>
+        <v>5827</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -6890,7 +6887,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>5756</v>
+        <v>5958</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -6955,7 +6952,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>5662</v>
+        <v>5864</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -7020,7 +7017,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>5709</v>
+        <v>5911</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -7077,7 +7074,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>5850</v>
+        <v>6052</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -7142,7 +7139,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>5395</v>
+        <v>5592</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -7207,7 +7204,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>5792</v>
+        <v>5994</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -7264,7 +7261,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>5499</v>
+        <v>5696</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -7321,7 +7318,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>5500</v>
+        <v>5697</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -7386,7 +7383,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>5501</v>
+        <v>5698</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -7445,7 +7442,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>5536</v>
+        <v>5733</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -7510,7 +7507,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>5537</v>
+        <v>5734</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -7637,7 +7634,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>5851</v>
+        <v>6053</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -7694,7 +7691,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>5902</v>
+        <v>6104</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -7751,7 +7748,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>5903</v>
+        <v>6105</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -7818,7 +7815,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>4140</v>
+        <v>4309</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -7879,7 +7876,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>4227</v>
+        <v>4396</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -7946,7 +7943,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>4172</v>
+        <v>4341</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -8006,7 +8003,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>4225</v>
+        <v>4394</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -8065,7 +8062,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>4226</v>
+        <v>4395</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -8132,7 +8129,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>4437</v>
+        <v>4606</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -8199,7 +8196,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>4476</v>
+        <v>4645</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -8262,7 +8259,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>4231</v>
+        <v>4400</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -8323,7 +8320,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>4272</v>
+        <v>4441</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -8386,7 +8383,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>4312</v>
+        <v>4481</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -8507,7 +8504,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>4854</v>
+        <v>5023</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -8560,11 +8557,11 @@
       <c r="N132" s="6" t="n"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>4892</v>
+        <v>5061</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -8621,7 +8618,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>4900</v>
+        <v>5097</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -8678,7 +8675,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>4904</v>
+        <v>5101</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -8737,7 +8734,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>4402</v>
+        <v>4571</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -8794,7 +8791,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>4937</v>
+        <v>5134</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -8851,7 +8848,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>4971</v>
+        <v>5168</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -8908,7 +8905,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>5005</v>
+        <v>5202</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -8975,7 +8972,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>4349</v>
+        <v>4518</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -9104,7 +9101,7 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>5038</v>
+        <v>5235</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -9161,7 +9158,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>5069</v>
+        <v>5266</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -9218,7 +9215,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>5070</v>
+        <v>5267</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -9283,7 +9280,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>5071</v>
+        <v>5268</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -9348,7 +9345,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>5111</v>
+        <v>5308</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -9407,7 +9404,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>4611</v>
+        <v>4780</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -9470,7 +9467,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>4517</v>
+        <v>4686</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -9533,7 +9530,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>4554</v>
+        <v>4723</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -9592,7 +9589,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>4586</v>
+        <v>4755</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -9651,7 +9648,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>4641</v>
+        <v>4810</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -9780,7 +9777,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>5152</v>
+        <v>5349</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -9837,7 +9834,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>5191</v>
+        <v>5388</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -9894,7 +9891,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>5266</v>
+        <v>5463</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -9951,7 +9948,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>5225</v>
+        <v>5422</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -10008,7 +10005,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>5229</v>
+        <v>5426</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -10065,7 +10062,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>5312</v>
+        <v>5509</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -10132,7 +10129,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>4709</v>
+        <v>4878</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -10189,7 +10186,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>5270</v>
+        <v>5467</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -10248,7 +10245,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>4717</v>
+        <v>4886</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -10305,7 +10302,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>4760</v>
+        <v>4929</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -10362,7 +10359,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>4799</v>
+        <v>4968</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -10419,7 +10416,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>4800</v>
+        <v>4969</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -10538,7 +10535,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>5313</v>
+        <v>5510</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -10595,7 +10592,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>5314</v>
+        <v>5511</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -10652,7 +10649,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>5315</v>
+        <v>5512</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -10709,7 +10706,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>4804</v>
+        <v>4973</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -10766,7 +10763,7 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>6391</v>
+        <v>6657</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -10823,7 +10820,7 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>6392</v>
+        <v>6658</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -10880,7 +10877,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>6393</v>
+        <v>6659</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -10937,7 +10934,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>6394</v>
+        <v>6660</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -10996,7 +10993,7 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>6386</v>
+        <v>6652</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -11053,7 +11050,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>6424</v>
+        <v>6690</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -11110,7 +11107,7 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>6455</v>
+        <v>6721</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -11167,7 +11164,7 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>6425</v>
+        <v>6691</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
@@ -11224,7 +11221,7 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>6426</v>
+        <v>6692</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -11281,7 +11278,7 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>6487</v>
+        <v>6753</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -11338,7 +11335,7 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>6387</v>
+        <v>6653</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -11397,7 +11394,7 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>6388</v>
+        <v>6654</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -11456,7 +11453,7 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>6389</v>
+        <v>6655</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -11515,7 +11512,7 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>6390</v>
+        <v>6656</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -11633,7 +11630,7 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1687</v>
+        <v>1708</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -11692,7 +11689,7 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1688</v>
+        <v>1709</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -11751,7 +11748,7 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2258</v>
+        <v>2309</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -11810,7 +11807,7 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1863</v>
+        <v>1884</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -11871,7 +11868,7 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1778</v>
+        <v>1799</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -11938,7 +11935,7 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2444</v>
+        <v>2495</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -12005,7 +12002,7 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>2533</v>
+        <v>2584</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -12072,7 +12069,7 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>2652</v>
+        <v>2703</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -12139,7 +12136,7 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2690</v>
+        <v>2741</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -12206,7 +12203,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2728</v>
+        <v>2779</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -12273,7 +12270,7 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2827</v>
+        <v>2878</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -12332,7 +12329,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2016</v>
+        <v>2067</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -12387,11 +12384,11 @@
       <c r="N196" s="6" t="n"/>
       <c r="O196" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -12450,7 +12447,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2017</v>
+        <v>2068</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
@@ -12573,7 +12570,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>2947</v>
+        <v>2998</v>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
@@ -12632,7 +12629,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2874</v>
+        <v>2925</v>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
@@ -12755,7 +12752,7 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>3099</v>
+        <v>3150</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
@@ -12814,7 +12811,7 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>3100</v>
+        <v>3151</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -12881,7 +12878,7 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2863</v>
+        <v>2914</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -12999,7 +12996,7 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>8007</v>
+        <v>8442</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -13060,7 +13057,7 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>7974</v>
+        <v>8409</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
@@ -13121,7 +13118,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>8010</v>
+        <v>8445</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -13182,7 +13179,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>8008</v>
+        <v>8443</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -13243,7 +13240,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>8009</v>
+        <v>8444</v>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
@@ -13302,7 +13299,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>7445</v>
+        <v>7794</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -13359,7 +13356,7 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>7593</v>
+        <v>7988</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -13418,7 +13415,7 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>7563</v>
+        <v>7912</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -13539,7 +13536,7 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>7594</v>
+        <v>7989</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -13596,7 +13593,7 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>7595</v>
+        <v>7990</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -13653,7 +13650,7 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>7596</v>
+        <v>7991</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -13710,7 +13707,7 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>7696</v>
+        <v>8091</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -13771,11 +13768,11 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P219" t="n">
-        <v>7568</v>
+        <v>7917</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -13834,7 +13831,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>7591</v>
+        <v>7986</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -13953,7 +13950,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>7772</v>
+        <v>8167</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -14010,7 +14007,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>7773</v>
+        <v>8168</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -14067,7 +14064,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>7836</v>
+        <v>8231</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -14126,7 +14123,7 @@
         </is>
       </c>
       <c r="P225" t="n">
-        <v>7837</v>
+        <v>8232</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -14183,7 +14180,7 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7839</v>
+        <v>8234</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -14240,7 +14237,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>7840</v>
+        <v>8235</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -14297,7 +14294,7 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>7838</v>
+        <v>8233</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
@@ -14356,7 +14353,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>7841</v>
+        <v>8236</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -14415,7 +14412,7 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>7829</v>
+        <v>8224</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -14472,7 +14469,7 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>7830</v>
+        <v>8225</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -14529,7 +14526,7 @@
         </is>
       </c>
       <c r="P232" t="n">
-        <v>7831</v>
+        <v>8226</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -14586,7 +14583,7 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>7832</v>
+        <v>8227</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -14645,7 +14642,7 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>7833</v>
+        <v>8228</v>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
@@ -14702,7 +14699,7 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>7834</v>
+        <v>8229</v>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
@@ -14761,7 +14758,7 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>7835</v>
+        <v>8230</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -14820,7 +14817,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>7842</v>
+        <v>8237</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -14877,7 +14874,7 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>7898</v>
+        <v>8333</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -14932,11 +14929,11 @@
       <c r="N239" s="3" t="n"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>7843</v>
+        <v>8238</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -15001,7 +14998,7 @@
         </is>
       </c>
       <c r="P240" t="n">
-        <v>7844</v>
+        <v>8279</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -15068,7 +15065,7 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>7850</v>
+        <v>8285</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
@@ -15133,7 +15130,7 @@
         </is>
       </c>
       <c r="P242" t="n">
-        <v>7892</v>
+        <v>8327</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -15198,7 +15195,7 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>7895</v>
+        <v>8330</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -15257,7 +15254,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>7808</v>
+        <v>8203</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -15314,7 +15311,7 @@
         </is>
       </c>
       <c r="P245" t="n">
-        <v>7809</v>
+        <v>8204</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -15371,7 +15368,7 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>7810</v>
+        <v>8205</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -15430,7 +15427,7 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>7811</v>
+        <v>8206</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -15549,7 +15546,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>7818</v>
+        <v>8213</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -15606,7 +15603,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>7821</v>
+        <v>8216</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -15663,7 +15660,7 @@
         </is>
       </c>
       <c r="P251" t="n">
-        <v>7819</v>
+        <v>8214</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -15720,7 +15717,7 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>7820</v>
+        <v>8215</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -15777,7 +15774,7 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>7823</v>
+        <v>8218</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -15834,7 +15831,7 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>7813</v>
+        <v>8208</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -15891,7 +15888,7 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>7822</v>
+        <v>8217</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -15948,7 +15945,7 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>7814</v>
+        <v>8209</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -16005,7 +16002,7 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>7815</v>
+        <v>8210</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -16126,7 +16123,7 @@
         </is>
       </c>
       <c r="P259" t="n">
-        <v>7824</v>
+        <v>8219</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -16183,7 +16180,7 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>7825</v>
+        <v>8220</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -16240,7 +16237,7 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>7826</v>
+        <v>8221</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
@@ -16297,7 +16294,7 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>7827</v>
+        <v>8222</v>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
@@ -16354,7 +16351,7 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>7828</v>
+        <v>8223</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -16419,7 +16416,7 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>6728</v>
+        <v>7034</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -16484,7 +16481,7 @@
         </is>
       </c>
       <c r="P265" t="n">
-        <v>6958</v>
+        <v>7307</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -16549,7 +16546,7 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>6995</v>
+        <v>7344</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -16614,7 +16611,7 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>7047</v>
+        <v>7396</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -16671,7 +16668,7 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>7107</v>
+        <v>7456</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
@@ -16728,7 +16725,7 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>7108</v>
+        <v>7457</v>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
@@ -16789,11 +16786,11 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>other SQL, no insert</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P270" t="n">
-        <v>6793</v>
+        <v>7118</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -16862,7 +16859,7 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>6732</v>
+        <v>7038</v>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -16927,11 +16924,11 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P272" t="n">
-        <v>6768</v>
+        <v>7074</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -16988,7 +16985,7 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>6784</v>
+        <v>7109</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -17055,7 +17052,7 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>6812</v>
+        <v>7161</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -17112,7 +17109,7 @@
         </is>
       </c>
       <c r="P275" t="n">
-        <v>7109</v>
+        <v>7458</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -17177,7 +17174,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>7110</v>
+        <v>7459</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -17242,7 +17239,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>7227</v>
+        <v>7576</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -17307,7 +17304,7 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>7152</v>
+        <v>7501</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -17364,7 +17361,7 @@
         </is>
       </c>
       <c r="P279" t="n">
-        <v>7226</v>
+        <v>7575</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -17421,7 +17418,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>7352</v>
+        <v>7701</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -17486,7 +17483,7 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>6854</v>
+        <v>7203</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -17551,7 +17548,7 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>7269</v>
+        <v>7618</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -17616,7 +17613,7 @@
         </is>
       </c>
       <c r="P283" t="n">
-        <v>6924</v>
+        <v>7273</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -17745,7 +17742,7 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>7353</v>
+        <v>7702</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -19061,7 +19058,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -19119,7 +19116,7 @@
         </is>
       </c>
       <c r="P313" t="n">
-        <v>1627</v>
+        <v>1648</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -19168,7 +19165,7 @@
         </is>
       </c>
       <c r="P314" t="n">
-        <v>1658</v>
+        <v>1679</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -19224,7 +19221,7 @@
         </is>
       </c>
       <c r="P315" t="n">
-        <v>1689</v>
+        <v>1710</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -19281,7 +19278,7 @@
         </is>
       </c>
       <c r="P316" t="n">
-        <v>1742</v>
+        <v>1763</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -19378,7 +19375,7 @@
         </is>
       </c>
       <c r="P318" t="n">
-        <v>1823</v>
+        <v>1844</v>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
@@ -19435,7 +19432,7 @@
         </is>
       </c>
       <c r="P319" t="n">
-        <v>1869</v>
+        <v>1890</v>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
@@ -19487,7 +19484,7 @@
         </is>
       </c>
       <c r="P320" t="n">
-        <v>1898</v>
+        <v>1919</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -19528,7 +19525,7 @@
         </is>
       </c>
       <c r="P321" t="n">
-        <v>1934</v>
+        <v>1955</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -19571,7 +19568,7 @@
         </is>
       </c>
       <c r="P322" t="n">
-        <v>1967</v>
+        <v>1988</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -19668,7 +19665,7 @@
         </is>
       </c>
       <c r="P324" t="n">
-        <v>2023</v>
+        <v>2074</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -19717,7 +19714,7 @@
         </is>
       </c>
       <c r="P325" t="n">
-        <v>2064</v>
+        <v>2115</v>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
@@ -19766,7 +19763,7 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>2101</v>
+        <v>2152</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -19812,7 +19809,7 @@
         </is>
       </c>
       <c r="P327" t="n">
-        <v>2138</v>
+        <v>2189</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -19861,7 +19858,7 @@
         </is>
       </c>
       <c r="P328" t="n">
-        <v>2182</v>
+        <v>2233</v>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
@@ -19907,7 +19904,7 @@
         </is>
       </c>
       <c r="P329" t="n">
-        <v>2230</v>
+        <v>2281</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -19953,7 +19950,7 @@
         </is>
       </c>
       <c r="P330" t="n">
-        <v>2264</v>
+        <v>2315</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -19999,7 +19996,7 @@
         </is>
       </c>
       <c r="P331" t="n">
-        <v>2292</v>
+        <v>2343</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -20045,7 +20042,7 @@
         </is>
       </c>
       <c r="P332" t="n">
-        <v>2327</v>
+        <v>2378</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -20091,7 +20088,7 @@
         </is>
       </c>
       <c r="P333" t="n">
-        <v>2356</v>
+        <v>2407</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -20137,7 +20134,7 @@
         </is>
       </c>
       <c r="P334" t="n">
-        <v>2385</v>
+        <v>2436</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -20183,7 +20180,7 @@
         </is>
       </c>
       <c r="P335" t="n">
-        <v>2414</v>
+        <v>2465</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -20239,7 +20236,7 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>2482</v>
+        <v>2533</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -20285,7 +20282,7 @@
         </is>
       </c>
       <c r="P337" t="n">
-        <v>2879</v>
+        <v>2930</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -20331,7 +20328,7 @@
         </is>
       </c>
       <c r="P338" t="n">
-        <v>2916</v>
+        <v>2967</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -20377,7 +20374,7 @@
         </is>
       </c>
       <c r="P339" t="n">
-        <v>2953</v>
+        <v>3004</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -20423,7 +20420,7 @@
         </is>
       </c>
       <c r="P340" t="n">
-        <v>2988</v>
+        <v>3039</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -20469,7 +20466,7 @@
         </is>
       </c>
       <c r="P341" t="n">
-        <v>3020</v>
+        <v>3071</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -20515,7 +20512,7 @@
         </is>
       </c>
       <c r="P342" t="n">
-        <v>3067</v>
+        <v>3118</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -20561,7 +20558,7 @@
         </is>
       </c>
       <c r="P343" t="n">
-        <v>3106</v>
+        <v>3157</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -20614,7 +20611,7 @@
         </is>
       </c>
       <c r="P344" t="n">
-        <v>3181</v>
+        <v>3232</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -20653,11 +20650,11 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P345" t="n">
-        <v>3267</v>
+        <v>3318</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -20715,7 +20712,7 @@
         </is>
       </c>
       <c r="P346" t="n">
-        <v>3978</v>
+        <v>4147</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -20769,11 +20766,11 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>count query</t>
+          <t>insert query</t>
         </is>
       </c>
       <c r="P347" t="n">
-        <v>5580</v>
+        <v>5777</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -20825,7 +20822,7 @@
         </is>
       </c>
       <c r="P348" t="n">
-        <v>6311</v>
+        <v>6577</v>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
@@ -20874,7 +20871,7 @@
         </is>
       </c>
       <c r="P349" t="n">
-        <v>6343</v>
+        <v>6609</v>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
@@ -20920,7 +20917,7 @@
         </is>
       </c>
       <c r="P350" t="n">
-        <v>6395</v>
+        <v>6661</v>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
@@ -20969,7 +20966,7 @@
         </is>
       </c>
       <c r="P351" t="n">
-        <v>6492</v>
+        <v>6758</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
@@ -21026,7 +21023,7 @@
         </is>
       </c>
       <c r="P352" t="n">
-        <v>6634</v>
+        <v>6940</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -21075,7 +21072,7 @@
         </is>
       </c>
       <c r="P353" t="n">
-        <v>6671</v>
+        <v>6977</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -21121,7 +21118,7 @@
         </is>
       </c>
       <c r="P354" t="n">
-        <v>6699</v>
+        <v>7005</v>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
@@ -21292,7 +21289,7 @@
         </is>
       </c>
       <c r="P357" t="n">
-        <v>7411</v>
+        <v>7760</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
@@ -21344,7 +21341,7 @@
         </is>
       </c>
       <c r="P358" t="n">
-        <v>7480</v>
+        <v>7829</v>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
@@ -21401,7 +21398,7 @@
         </is>
       </c>
       <c r="P359" t="n">
-        <v>7520</v>
+        <v>7869</v>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
@@ -21511,7 +21508,7 @@
         </is>
       </c>
       <c r="P361" t="n">
-        <v>7597</v>
+        <v>7992</v>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
@@ -21557,7 +21554,7 @@
         </is>
       </c>
       <c r="P362" t="n">
-        <v>7632</v>
+        <v>8027</v>
       </c>
       <c r="Q362" t="inlineStr">
         <is>
@@ -21603,7 +21600,7 @@
         </is>
       </c>
       <c r="P363" t="n">
-        <v>7661</v>
+        <v>8056</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -21649,7 +21646,7 @@
         </is>
       </c>
       <c r="P364" t="n">
-        <v>7700</v>
+        <v>8095</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -21695,7 +21692,7 @@
         </is>
       </c>
       <c r="P365" t="n">
-        <v>7735</v>
+        <v>8130</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -21743,7 +21740,7 @@
         </is>
       </c>
       <c r="P366" t="n">
-        <v>7817</v>
+        <v>8212</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -21792,7 +21789,7 @@
         </is>
       </c>
       <c r="P367" t="n">
-        <v>7899</v>
+        <v>8334</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -21849,7 +21846,7 @@
         </is>
       </c>
       <c r="P368" t="n">
-        <v>7927</v>
+        <v>8362</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -21898,7 +21895,7 @@
         </is>
       </c>
       <c r="P369" t="n">
-        <v>7979</v>
+        <v>8414</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -25587,7 +25584,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -25596,7 +25593,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -25647,13 +25644,13 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>12</v>
@@ -25677,10 +25674,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -25731,19 +25728,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -25797,13 +25794,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -25827,10 +25824,10 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -25857,13 +25854,13 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>16</v>
@@ -25887,10 +25884,10 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -26007,7 +26004,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -26016,7 +26013,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -26067,13 +26064,13 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>8</v>
@@ -26157,10 +26154,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
         <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -26177,22 +26174,22 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Missing_Event_Stream_Inserts.xlsx
+++ b/Missing_Event_Stream_Inserts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rapieruk-my.sharepoint.com/personal/ewan_hillnorris_rapieruk_com/Documents/Documents/GitHub/chillEpisodes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{4A26B38D-6BF2-49FB-9A2C-0721D01A6E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{08278EAB-B1FD-4E8D-A098-62D4DB43C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Code status summary" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing Inserts'!$A$1:$N$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing Inserts'!$A$1:$R$369</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -2703,6 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R369"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2780,7 +2781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>18</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -2862,7 +2863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>28</v>
       </c>
@@ -2900,7 +2901,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -2990,7 +2991,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -3080,7 +3081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
@@ -3123,7 +3124,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -3166,7 +3167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
@@ -3212,7 +3213,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -3255,7 +3256,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>18</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -3384,7 +3385,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -3429,7 +3430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3518,7 +3519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -3593,7 +3594,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P20">
         <v>6838</v>
@@ -3602,7 +3603,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -3636,7 +3637,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P21">
         <v>6839</v>
@@ -3645,7 +3646,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
@@ -3677,7 +3678,7 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P22">
         <v>6841</v>
@@ -3686,7 +3687,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
@@ -3718,7 +3719,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P23">
         <v>6840</v>
@@ -3727,7 +3728,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
@@ -3804,7 +3805,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P25">
         <v>6754</v>
@@ -3886,7 +3887,7 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P27">
         <v>6756</v>
@@ -3929,7 +3930,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P28">
         <v>6757</v>
@@ -4024,7 +4025,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>18</v>
       </c>
@@ -4067,7 +4068,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>18</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>18</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>18</v>
       </c>
@@ -4196,7 +4197,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>18</v>
       </c>
@@ -4243,7 +4244,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>18</v>
       </c>
@@ -4288,7 +4289,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>18</v>
       </c>
@@ -4333,7 +4334,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>28</v>
       </c>
@@ -4380,7 +4381,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>28</v>
       </c>
@@ -4425,7 +4426,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>28</v>
       </c>
@@ -4472,7 +4473,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>28</v>
       </c>
@@ -4517,7 +4518,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>28</v>
       </c>
@@ -4562,7 +4563,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>28</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>28</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>28</v>
       </c>
@@ -4691,7 +4692,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>28</v>
       </c>
@@ -4738,7 +4739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>28</v>
       </c>
@@ -4834,7 +4835,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>28</v>
       </c>
@@ -4881,7 +4882,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>28</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>28</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>28</v>
       </c>
@@ -5014,7 +5015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>28</v>
       </c>
@@ -5060,7 +5061,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>28</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>28</v>
       </c>
@@ -5152,7 +5153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>28</v>
       </c>
@@ -5200,7 +5201,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>28</v>
       </c>
@@ -5243,7 +5244,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
@@ -5290,7 +5291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>28</v>
       </c>
@@ -5337,7 +5338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>28</v>
       </c>
@@ -5384,7 +5385,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>28</v>
       </c>
@@ -5427,7 +5428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>28</v>
       </c>
@@ -5470,7 +5471,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>28</v>
       </c>
@@ -5517,7 +5518,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>28</v>
       </c>
@@ -5566,7 +5567,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>28</v>
       </c>
@@ -5609,7 +5610,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>28</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>28</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>28</v>
       </c>
@@ -5741,7 +5742,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>28</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>28</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>28</v>
       </c>
@@ -5870,7 +5871,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>28</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>28</v>
       </c>
@@ -5956,7 +5957,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>28</v>
       </c>
@@ -5988,7 +5989,7 @@
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
       <c r="O74" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P74">
         <v>6349</v>
@@ -5997,7 +5998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>28</v>
       </c>
@@ -6031,7 +6032,7 @@
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P75">
         <v>6350</v>
@@ -6040,7 +6041,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>28</v>
       </c>
@@ -6072,7 +6073,7 @@
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
       <c r="O76" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P76">
         <v>6352</v>
@@ -6081,7 +6082,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>28</v>
       </c>
@@ -6113,7 +6114,7 @@
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
       <c r="O77" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P77">
         <v>6351</v>
@@ -6122,7 +6123,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>28</v>
       </c>
@@ -6518,7 +6519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>28</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>28</v>
       </c>
@@ -6604,7 +6605,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>28</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>28</v>
       </c>
@@ -6686,7 +6687,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>28</v>
       </c>
@@ -6729,7 +6730,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>28</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>28</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>28</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>28</v>
       </c>
@@ -6913,7 +6914,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>28</v>
       </c>
@@ -6958,7 +6959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>28</v>
       </c>
@@ -7001,7 +7002,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>28</v>
       </c>
@@ -7042,7 +7043,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>28</v>
       </c>
@@ -7083,7 +7084,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>28</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>28</v>
       </c>
@@ -7175,7 +7176,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>28</v>
       </c>
@@ -7220,7 +7221,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>28</v>
       </c>
@@ -7270,7 +7271,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>28</v>
       </c>
@@ -7315,7 +7316,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>28</v>
       </c>
@@ -7360,7 +7361,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>28</v>
       </c>
@@ -7405,7 +7406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>28</v>
       </c>
@@ -7450,7 +7451,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>28</v>
       </c>
@@ -7491,7 +7492,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>28</v>
       </c>
@@ -7536,7 +7537,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>28</v>
       </c>
@@ -7581,7 +7582,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>28</v>
       </c>
@@ -7622,7 +7623,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>28</v>
       </c>
@@ -7663,7 +7664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -7708,7 +7709,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>28</v>
       </c>
@@ -7751,7 +7752,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>28</v>
       </c>
@@ -7796,7 +7797,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>28</v>
       </c>
@@ -7840,7 +7841,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>28</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>28</v>
       </c>
@@ -7926,7 +7927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>28</v>
       </c>
@@ -7967,7 +7968,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>28</v>
       </c>
@@ -8014,7 +8015,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>28</v>
       </c>
@@ -8059,7 +8060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>28</v>
       </c>
@@ -8106,7 +8107,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>28</v>
       </c>
@@ -8149,7 +8150,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>28</v>
       </c>
@@ -8192,7 +8193,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>28</v>
       </c>
@@ -8239,7 +8240,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>28</v>
       </c>
@@ -8286,7 +8287,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>28</v>
       </c>
@@ -8333,7 +8334,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>28</v>
       </c>
@@ -8378,7 +8379,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>28</v>
       </c>
@@ -8425,7 +8426,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>28</v>
       </c>
@@ -8471,7 +8472,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>28</v>
       </c>
@@ -8512,7 +8513,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>28</v>
       </c>
@@ -8553,7 +8554,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>28</v>
       </c>
@@ -8594,7 +8595,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>28</v>
       </c>
@@ -8635,7 +8636,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>28</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>28</v>
       </c>
@@ -8719,7 +8720,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>28</v>
       </c>
@@ -8760,7 +8761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>28</v>
       </c>
@@ -8801,7 +8802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>28</v>
       </c>
@@ -8848,7 +8849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>28</v>
       </c>
@@ -8898,7 +8899,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>28</v>
       </c>
@@ -8939,7 +8940,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>28</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>28</v>
       </c>
@@ -9021,7 +9022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>28</v>
       </c>
@@ -9066,7 +9067,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>28</v>
       </c>
@@ -9111,7 +9112,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>28</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>28</v>
       </c>
@@ -9201,7 +9202,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>28</v>
       </c>
@@ -9248,7 +9249,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
         <v>28</v>
       </c>
@@ -9291,7 +9292,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
         <v>28</v>
       </c>
@@ -9334,7 +9335,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
         <v>28</v>
       </c>
@@ -9384,7 +9385,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
         <v>28</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
         <v>28</v>
       </c>
@@ -9466,7 +9467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
         <v>28</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
         <v>28</v>
       </c>
@@ -9548,7 +9549,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>28</v>
       </c>
@@ -9589,7 +9590,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>28</v>
       </c>
@@ -9630,7 +9631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
         <v>28</v>
       </c>
@@ -9677,7 +9678,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>28</v>
       </c>
@@ -9718,7 +9719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>28</v>
       </c>
@@ -9761,7 +9762,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>28</v>
       </c>
@@ -9802,7 +9803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>28</v>
       </c>
@@ -9843,7 +9844,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>28</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
         <v>28</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>28</v>
       </c>
@@ -9969,7 +9970,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>28</v>
       </c>
@@ -10010,7 +10011,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>28</v>
       </c>
@@ -10051,7 +10052,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>28</v>
       </c>
@@ -10092,7 +10093,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>18</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>18</v>
       </c>
@@ -10174,7 +10175,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>18</v>
       </c>
@@ -10215,7 +10216,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>18</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>18</v>
       </c>
@@ -10299,7 +10300,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10341,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>18</v>
       </c>
@@ -10381,7 +10382,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
         <v>18</v>
       </c>
@@ -10422,7 +10423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>18</v>
       </c>
@@ -10463,7 +10464,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>18</v>
       </c>
@@ -10504,7 +10505,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
         <v>18</v>
       </c>
@@ -10545,7 +10546,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>18</v>
       </c>
@@ -10588,7 +10589,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>18</v>
       </c>
@@ -10631,7 +10632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>18</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>18</v>
       </c>
@@ -10717,7 +10718,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>18</v>
       </c>
@@ -10760,7 +10761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>18</v>
       </c>
@@ -10803,7 +10804,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>18</v>
       </c>
@@ -10846,7 +10847,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
         <v>18</v>
       </c>
@@ -10889,7 +10890,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>18</v>
       </c>
@@ -10934,7 +10935,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
         <v>18</v>
       </c>
@@ -10981,7 +10982,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
         <v>18</v>
       </c>
@@ -11028,7 +11029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
         <v>18</v>
       </c>
@@ -11075,7 +11076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
         <v>18</v>
       </c>
@@ -11122,7 +11123,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
         <v>18</v>
       </c>
@@ -11169,7 +11170,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
         <v>18</v>
       </c>
@@ -11216,7 +11217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
         <v>18</v>
       </c>
@@ -11259,7 +11260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
         <v>18</v>
       </c>
@@ -11302,7 +11303,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
         <v>18</v>
       </c>
@@ -11345,7 +11346,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="5" t="s">
         <v>18</v>
       </c>
@@ -11391,7 +11392,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
         <v>18</v>
       </c>
@@ -11434,7 +11435,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
         <v>18</v>
       </c>
@@ -11477,7 +11478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>18</v>
       </c>
@@ -11523,7 +11524,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
         <v>18</v>
       </c>
@@ -11566,7 +11567,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
         <v>18</v>
       </c>
@@ -11609,7 +11610,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
         <v>18</v>
       </c>
@@ -11656,7 +11657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>18</v>
       </c>
@@ -11699,7 +11700,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5" t="s">
         <v>25</v>
       </c>
@@ -11733,7 +11734,7 @@
       <c r="M206" s="5"/>
       <c r="N206" s="5"/>
       <c r="O206" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P206">
         <v>8442</v>
@@ -11742,7 +11743,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>25</v>
       </c>
@@ -11787,7 +11788,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>25</v>
       </c>
@@ -11832,7 +11833,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>25</v>
       </c>
@@ -11877,7 +11878,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>25</v>
       </c>
@@ -11922,7 +11923,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
         <v>445</v>
       </c>
@@ -11965,7 +11966,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>445</v>
       </c>
@@ -12006,7 +12007,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>445</v>
       </c>
@@ -12049,7 +12050,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>445</v>
       </c>
@@ -12095,7 +12096,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
         <v>445</v>
       </c>
@@ -12136,7 +12137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>445</v>
       </c>
@@ -12177,7 +12178,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
         <v>445</v>
       </c>
@@ -12218,7 +12219,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
         <v>445</v>
       </c>
@@ -12259,7 +12260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
         <v>445</v>
       </c>
@@ -12304,7 +12305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>445</v>
       </c>
@@ -12347,7 +12348,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>445</v>
       </c>
@@ -12391,7 +12392,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="5" t="s">
         <v>445</v>
       </c>
@@ -12432,7 +12433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
         <v>445</v>
       </c>
@@ -12473,7 +12474,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="5" t="s">
         <v>445</v>
       </c>
@@ -12505,7 +12506,7 @@
       <c r="M224" s="5"/>
       <c r="N224" s="5"/>
       <c r="O224" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P224">
         <v>8231</v>
@@ -12514,7 +12515,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>445</v>
       </c>
@@ -12548,7 +12549,7 @@
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
       <c r="O225" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P225">
         <v>8232</v>
@@ -12557,7 +12558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="5" t="s">
         <v>445</v>
       </c>
@@ -12589,7 +12590,7 @@
       <c r="M226" s="5"/>
       <c r="N226" s="5"/>
       <c r="O226" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P226">
         <v>8234</v>
@@ -12598,7 +12599,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>445</v>
       </c>
@@ -12639,7 +12640,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>445</v>
       </c>
@@ -12671,7 +12672,7 @@
       <c r="M228" s="5"/>
       <c r="N228" s="5"/>
       <c r="O228" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P228">
         <v>8233</v>
@@ -12680,7 +12681,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>445</v>
       </c>
@@ -12757,7 +12758,7 @@
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
       <c r="O230" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P230">
         <v>8224</v>
@@ -12839,7 +12840,7 @@
       <c r="M232" s="5"/>
       <c r="N232" s="5"/>
       <c r="O232" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P232">
         <v>8226</v>
@@ -12880,7 +12881,7 @@
       <c r="M233" s="5"/>
       <c r="N233" s="5"/>
       <c r="O233" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P233">
         <v>8227</v>
@@ -12923,7 +12924,7 @@
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
       <c r="O234" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P234">
         <v>8228</v>
@@ -13016,7 +13017,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>445</v>
       </c>
@@ -13059,7 +13060,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>445</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>445</v>
       </c>
@@ -13143,7 +13144,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>445</v>
       </c>
@@ -13188,7 +13189,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>445</v>
       </c>
@@ -13235,7 +13236,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
         <v>445</v>
       </c>
@@ -13280,7 +13281,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
         <v>445</v>
       </c>
@@ -13325,7 +13326,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>445</v>
       </c>
@@ -13368,7 +13369,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
         <v>445</v>
       </c>
@@ -13409,7 +13410,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="5" t="s">
         <v>445</v>
       </c>
@@ -13450,7 +13451,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>445</v>
       </c>
@@ -13493,7 +13494,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>445</v>
       </c>
@@ -13537,7 +13538,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="5" t="s">
         <v>445</v>
       </c>
@@ -13578,7 +13579,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="5" t="s">
         <v>445</v>
       </c>
@@ -13619,7 +13620,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="5" t="s">
         <v>445</v>
       </c>
@@ -13660,7 +13661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="5" t="s">
         <v>445</v>
       </c>
@@ -13701,7 +13702,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>445</v>
       </c>
@@ -13742,7 +13743,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="5" t="s">
         <v>445</v>
       </c>
@@ -13783,7 +13784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>445</v>
       </c>
@@ -13824,7 +13825,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>445</v>
       </c>
@@ -13865,7 +13866,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="5" t="s">
         <v>445</v>
       </c>
@@ -13906,7 +13907,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>445</v>
       </c>
@@ -13952,7 +13953,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
         <v>445</v>
       </c>
@@ -13993,7 +13994,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="5" t="s">
         <v>445</v>
       </c>
@@ -14034,7 +14035,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>445</v>
       </c>
@@ -14075,7 +14076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="5" t="s">
         <v>445</v>
       </c>
@@ -14116,7 +14117,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>445</v>
       </c>
@@ -14157,7 +14158,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>445</v>
       </c>
@@ -14204,7 +14205,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>445</v>
       </c>
@@ -14249,7 +14250,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="5" t="s">
         <v>445</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="5" t="s">
         <v>445</v>
       </c>
@@ -14339,7 +14340,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
         <v>445</v>
       </c>
@@ -14380,7 +14381,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
         <v>445</v>
       </c>
@@ -14421,7 +14422,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>445</v>
       </c>
@@ -14466,7 +14467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>445</v>
       </c>
@@ -14515,7 +14516,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>445</v>
       </c>
@@ -14564,7 +14565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
         <v>445</v>
       </c>
@@ -14605,7 +14606,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>445</v>
       </c>
@@ -14652,7 +14653,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="5" t="s">
         <v>445</v>
       </c>
@@ -14693,7 +14694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5" t="s">
         <v>445</v>
       </c>
@@ -14738,7 +14739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
         <v>445</v>
       </c>
@@ -14783,7 +14784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="5" t="s">
         <v>445</v>
       </c>
@@ -14828,7 +14829,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>445</v>
       </c>
@@ -14869,7 +14870,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>445</v>
       </c>
@@ -14910,7 +14911,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
         <v>445</v>
       </c>
@@ -14955,7 +14956,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
         <v>445</v>
       </c>
@@ -15000,7 +15001,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="5" t="s">
         <v>445</v>
       </c>
@@ -15045,7 +15046,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>445</v>
       </c>
@@ -15091,7 +15092,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>445</v>
       </c>
@@ -15136,7 +15137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -15177,7 +15178,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -15206,7 +15207,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -15244,7 +15245,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -15279,7 +15280,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -15311,7 +15312,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -15343,7 +15344,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -15384,7 +15385,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -15416,7 +15417,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -15451,7 +15452,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -15492,7 +15493,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -15533,7 +15534,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -15568,7 +15569,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -15600,7 +15601,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -15632,7 +15633,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -15670,7 +15671,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -15705,7 +15706,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -15743,7 +15744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -15778,7 +15779,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>18</v>
       </c>
@@ -15810,7 +15811,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -15842,7 +15843,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -15874,7 +15875,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -15906,7 +15907,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -15938,7 +15939,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -15970,7 +15971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -16002,7 +16003,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -16034,7 +16035,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -16066,7 +16067,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -16104,7 +16105,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -16139,7 +16140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -16177,7 +16178,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -16218,7 +16219,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -16253,7 +16254,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -16285,7 +16286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -16326,7 +16327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -16364,7 +16365,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>18</v>
       </c>
@@ -16393,7 +16394,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>18</v>
       </c>
@@ -16422,7 +16423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>18</v>
       </c>
@@ -16457,7 +16458,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>18</v>
       </c>
@@ -16489,7 +16490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>18</v>
       </c>
@@ -16524,7 +16525,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>18</v>
       </c>
@@ -16559,7 +16560,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>18</v>
       </c>
@@ -16591,7 +16592,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>18</v>
       </c>
@@ -16626,7 +16627,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>18</v>
       </c>
@@ -16658,7 +16659,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>18</v>
       </c>
@@ -16690,7 +16691,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>18</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>18</v>
       </c>
@@ -16754,7 +16755,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>18</v>
       </c>
@@ -16786,7 +16787,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>18</v>
       </c>
@@ -16818,7 +16819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>18</v>
       </c>
@@ -16850,7 +16851,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>18</v>
       </c>
@@ -16888,7 +16889,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>18</v>
       </c>
@@ -16920,7 +16921,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>18</v>
       </c>
@@ -16952,7 +16953,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>18</v>
       </c>
@@ -16984,7 +16985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>18</v>
       </c>
@@ -17016,7 +17017,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>18</v>
       </c>
@@ -17048,7 +17049,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>18</v>
       </c>
@@ -17080,7 +17081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>18</v>
       </c>
@@ -17112,7 +17113,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>28</v>
       </c>
@@ -17147,7 +17148,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>28</v>
       </c>
@@ -17176,7 +17177,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>28</v>
       </c>
@@ -17214,7 +17215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>28</v>
       </c>
@@ -17252,7 +17253,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>18</v>
       </c>
@@ -17290,7 +17291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>18</v>
       </c>
@@ -17325,7 +17326,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>18</v>
       </c>
@@ -17392,7 +17393,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>445</v>
       </c>
@@ -17433,7 +17434,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>445</v>
       </c>
@@ -17468,7 +17469,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>445</v>
       </c>
@@ -17500,7 +17501,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>445</v>
       </c>
@@ -17535,7 +17536,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>445</v>
       </c>
@@ -17576,7 +17577,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>445</v>
       </c>
@@ -17617,7 +17618,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>445</v>
       </c>
@@ -17655,7 +17656,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>445</v>
       </c>
@@ -17696,7 +17697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>445</v>
       </c>
@@ -17731,7 +17732,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>445</v>
       </c>
@@ -17772,7 +17773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>445</v>
       </c>
@@ -17804,7 +17805,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>445</v>
       </c>
@@ -17836,7 +17837,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>445</v>
       </c>
@@ -17868,7 +17869,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>445</v>
       </c>
@@ -17900,7 +17901,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>445</v>
       </c>
@@ -17932,7 +17933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>25</v>
       </c>
@@ -17967,7 +17968,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>25</v>
       </c>
@@ -18008,7 +18009,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>25</v>
       </c>
@@ -18044,10 +18045,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N285" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N285">
-      <sortCondition ref="C1:C285"/>
-    </sortState>
+  <autoFilter ref="A1:R369" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Cancellation"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Missing_Event_Stream_Inserts.xlsx
+++ b/Missing_Event_Stream_Inserts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rapieruk-my.sharepoint.com/personal/ewan_hillnorris_rapieruk_com/Documents/Documents/GitHub/chillEpisodes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{08278EAB-B1FD-4E8D-A098-62D4DB43C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="14_{08278EAB-B1FD-4E8D-A098-62D4DB43C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD0BFBA-294C-48A8-877A-FE1D562006E4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing Inserts'!$A$1:$R$369</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3651" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3652" uniqueCount="750">
   <si>
     <t>Product</t>
   </si>
@@ -2289,6 +2288,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>HR1a,HR1b</t>
   </si>
 </sst>
 </file>
@@ -2991,7 +2993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -3038,7 +3040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -3124,7 +3126,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -3213,7 +3215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -3256,7 +3258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>18</v>
       </c>
@@ -3299,7 +3301,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
@@ -3342,7 +3344,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -3476,7 +3478,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3519,7 +3521,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -3728,7 +3730,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
@@ -3771,7 +3773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -3855,7 +3857,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>18</v>
       </c>
@@ -3896,7 +3898,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -3939,7 +3941,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
@@ -3973,7 +3975,7 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P29">
         <v>6836</v>
@@ -4025,7 +4027,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>18</v>
       </c>
@@ -4068,7 +4070,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>18</v>
       </c>
@@ -4152,7 +4154,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>18</v>
       </c>
@@ -4244,7 +4246,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>18</v>
       </c>
@@ -4289,7 +4291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>18</v>
       </c>
@@ -4563,7 +4565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>28</v>
       </c>
@@ -4739,7 +4741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -4882,7 +4884,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>28</v>
       </c>
@@ -5201,7 +5203,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>28</v>
       </c>
@@ -5385,7 +5387,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>28</v>
       </c>
@@ -5428,7 +5430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>28</v>
       </c>
@@ -5656,7 +5658,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>28</v>
       </c>
@@ -5699,7 +5701,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>28</v>
       </c>
@@ -5828,7 +5830,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>28</v>
       </c>
@@ -5871,7 +5873,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>28</v>
       </c>
@@ -5914,7 +5916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>28</v>
       </c>
@@ -6123,7 +6125,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>28</v>
       </c>
@@ -6166,7 +6168,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>28</v>
       </c>
@@ -6211,7 +6213,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>28</v>
       </c>
@@ -6252,7 +6254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>28</v>
       </c>
@@ -6294,7 +6296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>28</v>
       </c>
@@ -6339,7 +6341,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>28</v>
       </c>
@@ -6384,7 +6386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>28</v>
       </c>
@@ -6431,7 +6433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>28</v>
       </c>
@@ -6519,7 +6521,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>28</v>
       </c>
@@ -6562,7 +6564,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>28</v>
       </c>
@@ -6605,7 +6607,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>28</v>
       </c>
@@ -6646,7 +6648,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>28</v>
       </c>
@@ -6687,7 +6689,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>28</v>
       </c>
@@ -6959,7 +6961,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>28</v>
       </c>
@@ -7002,7 +7004,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>28</v>
       </c>
@@ -7043,7 +7045,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>28</v>
       </c>
@@ -7451,7 +7453,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>28</v>
       </c>
@@ -7582,7 +7584,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>28</v>
       </c>
@@ -7623,7 +7625,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>28</v>
       </c>
@@ -7709,7 +7711,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>28</v>
       </c>
@@ -7886,7 +7888,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>28</v>
       </c>
@@ -7927,7 +7929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>28</v>
       </c>
@@ -8051,13 +8053,16 @@
       <c r="M121" s="5"/>
       <c r="N121" s="5"/>
       <c r="O121" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="P121">
         <v>4396</v>
       </c>
       <c r="Q121" t="s">
-        <v>37</v>
+        <v>53</v>
+      </c>
+      <c r="R121" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
@@ -8107,7 +8112,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>28</v>
       </c>
@@ -8150,7 +8155,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>28</v>
       </c>
@@ -8554,7 +8559,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>28</v>
       </c>
@@ -8940,7 +8945,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>28</v>
       </c>
@@ -8981,7 +8986,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>28</v>
       </c>
@@ -9249,7 +9254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
         <v>28</v>
       </c>
@@ -9467,7 +9472,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
         <v>28</v>
       </c>
@@ -9508,7 +9513,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
         <v>28</v>
       </c>
@@ -9590,7 +9595,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>28</v>
       </c>
@@ -9631,7 +9636,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
         <v>28</v>
       </c>
@@ -9803,7 +9808,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>28</v>
       </c>
@@ -9844,7 +9849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>28</v>
       </c>
@@ -9929,7 +9934,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>28</v>
       </c>
@@ -9970,7 +9975,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>28</v>
       </c>
@@ -10011,7 +10016,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>28</v>
       </c>
@@ -10093,7 +10098,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>18</v>
       </c>
@@ -10134,7 +10139,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>18</v>
       </c>
@@ -10175,7 +10180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>18</v>
       </c>
@@ -10216,7 +10221,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>18</v>
       </c>
@@ -10257,7 +10262,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>18</v>
       </c>
@@ -10300,7 +10305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>18</v>
       </c>
@@ -10382,7 +10387,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
         <v>18</v>
       </c>
@@ -10464,7 +10469,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>18</v>
       </c>
@@ -10505,7 +10510,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
         <v>18</v>
       </c>
@@ -10546,7 +10551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>18</v>
       </c>
@@ -10589,7 +10594,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>18</v>
       </c>
@@ -10632,7 +10637,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>18</v>
       </c>
@@ -10675,7 +10680,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>18</v>
       </c>
@@ -10718,7 +10723,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>18</v>
       </c>
@@ -10761,7 +10766,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>18</v>
       </c>
@@ -10804,7 +10809,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>18</v>
       </c>
@@ -10847,7 +10852,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
         <v>18</v>
       </c>
@@ -11217,7 +11222,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
         <v>18</v>
       </c>
@@ -11303,7 +11308,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
         <v>18</v>
       </c>
@@ -11392,7 +11397,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
         <v>18</v>
       </c>
@@ -11435,7 +11440,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
         <v>18</v>
       </c>
@@ -11524,7 +11529,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
         <v>18</v>
       </c>
@@ -11567,7 +11572,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
         <v>18</v>
       </c>
@@ -11610,7 +11615,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
         <v>18</v>
       </c>
@@ -11657,7 +11662,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>18</v>
       </c>
@@ -11788,7 +11793,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>25</v>
       </c>
@@ -11833,7 +11838,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>25</v>
       </c>
@@ -11878,7 +11883,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>25</v>
       </c>
@@ -11966,7 +11971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>445</v>
       </c>
@@ -12007,7 +12012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>445</v>
       </c>
@@ -12096,7 +12101,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
         <v>445</v>
       </c>
@@ -12137,7 +12142,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>445</v>
       </c>
@@ -12178,7 +12183,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
         <v>445</v>
       </c>
@@ -12219,7 +12224,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
         <v>445</v>
       </c>
@@ -12305,7 +12310,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>445</v>
       </c>
@@ -12392,7 +12397,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A222" s="5" t="s">
         <v>445</v>
       </c>
@@ -12599,7 +12604,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>445</v>
       </c>
@@ -12681,7 +12686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>445</v>
       </c>
@@ -12724,7 +12729,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>445</v>
       </c>
@@ -12808,7 +12813,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="5" t="s">
         <v>445</v>
       </c>
@@ -12849,7 +12854,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
         <v>445</v>
       </c>
@@ -12890,7 +12895,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>445</v>
       </c>
@@ -12933,7 +12938,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
         <v>445</v>
       </c>
@@ -12965,7 +12970,7 @@
       <c r="M235" s="5"/>
       <c r="N235" s="5"/>
       <c r="O235" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P235">
         <v>8229</v>
@@ -13017,7 +13022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>445</v>
       </c>
@@ -13060,7 +13065,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>445</v>
       </c>
@@ -13144,7 +13149,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>445</v>
       </c>
@@ -13236,7 +13241,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
         <v>445</v>
       </c>
@@ -13281,7 +13286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
         <v>445</v>
       </c>
@@ -13360,7 +13365,7 @@
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
       <c r="O244" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P244">
         <v>8203</v>
@@ -13401,7 +13406,7 @@
       <c r="M245" s="5"/>
       <c r="N245" s="5"/>
       <c r="O245" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P245">
         <v>8204</v>
@@ -13410,7 +13415,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A246" s="5" t="s">
         <v>445</v>
       </c>
@@ -13485,7 +13490,7 @@
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
       <c r="O247" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P247">
         <v>8206</v>
@@ -13570,7 +13575,7 @@
       <c r="M249" s="5"/>
       <c r="N249" s="5"/>
       <c r="O249" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P249">
         <v>8213</v>
@@ -13611,7 +13616,7 @@
       <c r="M250" s="5"/>
       <c r="N250" s="5"/>
       <c r="O250" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P250">
         <v>8216</v>
@@ -13652,7 +13657,7 @@
       <c r="M251" s="5"/>
       <c r="N251" s="5"/>
       <c r="O251" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P251">
         <v>8214</v>
@@ -13661,7 +13666,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A252" s="5" t="s">
         <v>445</v>
       </c>
@@ -13702,7 +13707,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>445</v>
       </c>
@@ -13775,7 +13780,7 @@
       <c r="M254" s="5"/>
       <c r="N254" s="5"/>
       <c r="O254" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P254">
         <v>8208</v>
@@ -13816,7 +13821,7 @@
       <c r="M255" s="5"/>
       <c r="N255" s="5"/>
       <c r="O255" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P255">
         <v>8217</v>
@@ -13825,7 +13830,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>445</v>
       </c>
@@ -13898,7 +13903,7 @@
       <c r="M257" s="5"/>
       <c r="N257" s="5"/>
       <c r="O257" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P257">
         <v>8210</v>
@@ -13953,7 +13958,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
         <v>445</v>
       </c>
@@ -13994,7 +13999,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A260" s="5" t="s">
         <v>445</v>
       </c>
@@ -14035,7 +14040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>445</v>
       </c>
@@ -14076,7 +14081,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A262" s="5" t="s">
         <v>445</v>
       </c>
@@ -14117,7 +14122,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>445</v>
       </c>
@@ -14158,7 +14163,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>445</v>
       </c>
@@ -14340,7 +14345,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
         <v>445</v>
       </c>
@@ -14381,7 +14386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
         <v>445</v>
       </c>
@@ -14565,7 +14570,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
         <v>445</v>
       </c>
@@ -14606,7 +14611,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>445</v>
       </c>
@@ -14685,7 +14690,7 @@
       <c r="M275" s="5"/>
       <c r="N275" s="5"/>
       <c r="O275" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P275">
         <v>7458</v>
@@ -14829,7 +14834,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>445</v>
       </c>
@@ -14870,7 +14875,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>445</v>
       </c>
@@ -17358,7 +17363,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>18</v>
       </c>
@@ -17901,7 +17906,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>445</v>
       </c>
@@ -18046,9 +18051,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R369" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="14">
       <filters>
-        <filter val="Cancellation"/>
+        <filter val="empty"/>
       </filters>
     </filterColumn>
   </autoFilter>
